--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFB8AA1-34F3-4154-910C-E9FB8FDE6C14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1DAA7A-A263-4CE1-9DCF-DB13D4EDDF88}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="98">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -249,13 +249,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スキル発動時</t>
-    <rPh sb="3" eb="6">
-      <t>ハツドウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ボタンで発動</t>
     <rPh sb="4" eb="6">
       <t>ハツドウ</t>
@@ -273,18 +266,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>skillArcana</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>commandArcana</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>startArcana</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HPを1.3倍にしてくれるカード</t>
     <rPh sb="6" eb="7">
       <t>バイ</t>
@@ -564,6 +545,56 @@
   </si>
   <si>
     <t>Back</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Command</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SkillEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DamageEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DeathEffect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル発動時に発動</t>
+    <rPh sb="3" eb="5">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージで発動</t>
+    <rPh sb="5" eb="7">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡時に発動</t>
+    <rPh sb="0" eb="3">
+      <t>シボウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハツドウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -682,14 +713,14 @@
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="7">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
-      <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="0">
+      <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
@@ -703,7 +734,7 @@
     <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="0">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -718,7 +749,7 @@
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="1">
       <calculatedColumnFormula>IF(ArcanaMaster[[#This Row],[位置]]="Front", "正位置", "逆位置")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
@@ -1585,7 +1616,7 @@
         <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1602,8 +1633,8 @@
         <v>愚者</v>
       </c>
       <c r="D2" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E2">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1640,8 +1671,8 @@
         <v>愚者</v>
       </c>
       <c r="D3" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E3">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1678,8 +1709,8 @@
         <v>魔術師</v>
       </c>
       <c r="D4" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E4">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1716,8 +1747,8 @@
         <v>魔術師</v>
       </c>
       <c r="D5" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E5">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1754,8 +1785,8 @@
         <v>女教皇</v>
       </c>
       <c r="D6" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E6">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1792,8 +1823,8 @@
         <v>女教皇</v>
       </c>
       <c r="D7" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E7">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1830,8 +1861,8 @@
         <v>女帝</v>
       </c>
       <c r="D8" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E8">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1868,8 +1899,8 @@
         <v>女帝</v>
       </c>
       <c r="D9" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E9">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1906,8 +1937,8 @@
         <v>皇帝</v>
       </c>
       <c r="D10" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E10">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1944,8 +1975,8 @@
         <v>皇帝</v>
       </c>
       <c r="D11" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E11">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -1982,8 +2013,8 @@
         <v>教皇</v>
       </c>
       <c r="D12" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E12">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2020,8 +2051,8 @@
         <v>教皇</v>
       </c>
       <c r="D13" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E13">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2058,8 +2089,8 @@
         <v>恋人</v>
       </c>
       <c r="D14" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E14">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2096,8 +2127,8 @@
         <v>恋人</v>
       </c>
       <c r="D15" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E15">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2134,8 +2165,8 @@
         <v>戦車</v>
       </c>
       <c r="D16" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E16">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2172,8 +2203,8 @@
         <v>戦車</v>
       </c>
       <c r="D17" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E17">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2210,8 +2241,8 @@
         <v>力</v>
       </c>
       <c r="D18" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E18">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2248,8 +2279,8 @@
         <v>力</v>
       </c>
       <c r="D19" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E19">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2286,8 +2317,8 @@
         <v>隠者</v>
       </c>
       <c r="D20" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E20">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2324,8 +2355,8 @@
         <v>隠者</v>
       </c>
       <c r="D21" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E21">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2362,8 +2393,8 @@
         <v>運命の輪</v>
       </c>
       <c r="D22" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E22">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2400,8 +2431,8 @@
         <v>運命の輪</v>
       </c>
       <c r="D23" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E23">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2438,8 +2469,8 @@
         <v>正義</v>
       </c>
       <c r="D24" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E24">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2476,8 +2507,8 @@
         <v>正義</v>
       </c>
       <c r="D25" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E25">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2514,8 +2545,8 @@
         <v>つるされた男</v>
       </c>
       <c r="D26" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E26">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2552,8 +2583,8 @@
         <v>つるされた男</v>
       </c>
       <c r="D27" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E27">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2590,8 +2621,8 @@
         <v>死神</v>
       </c>
       <c r="D28" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E28">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2628,8 +2659,8 @@
         <v>死神</v>
       </c>
       <c r="D29" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E29">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2666,8 +2697,8 @@
         <v>節制</v>
       </c>
       <c r="D30" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E30">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2704,8 +2735,8 @@
         <v>節制</v>
       </c>
       <c r="D31" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E31">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2742,8 +2773,8 @@
         <v>悪魔</v>
       </c>
       <c r="D32" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E32">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2780,8 +2811,8 @@
         <v>悪魔</v>
       </c>
       <c r="D33" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E33">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2818,8 +2849,8 @@
         <v>塔</v>
       </c>
       <c r="D34" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E34">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2856,8 +2887,8 @@
         <v>塔</v>
       </c>
       <c r="D35" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E35">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2894,8 +2925,8 @@
         <v>星</v>
       </c>
       <c r="D36" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E36">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2932,8 +2963,8 @@
         <v>星</v>
       </c>
       <c r="D37" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E37">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2970,8 +3001,8 @@
         <v>月</v>
       </c>
       <c r="D38" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E38">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3008,8 +3039,8 @@
         <v>月</v>
       </c>
       <c r="D39" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E39">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3046,8 +3077,8 @@
         <v>太陽</v>
       </c>
       <c r="D40" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E40">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3084,8 +3115,8 @@
         <v>太陽</v>
       </c>
       <c r="D41" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E41">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3122,8 +3153,8 @@
         <v>審判</v>
       </c>
       <c r="D42" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E42">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3160,8 +3191,8 @@
         <v>審判</v>
       </c>
       <c r="D43" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E43">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3198,8 +3229,8 @@
         <v>世界</v>
       </c>
       <c r="D44" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E44">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3236,8 +3267,8 @@
         <v>世界</v>
       </c>
       <c r="D45" t="str">
-        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$4,2,FALSE)</f>
-        <v>skillArcana</v>
+        <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
+        <v>StartEffect</v>
       </c>
       <c r="E45">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3275,7 +3306,7 @@
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.296875" bestFit="1" customWidth="1"/>
@@ -3289,41 +3320,41 @@
       </c>
       <c r="B1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E1" s="2"/>
       <c r="G1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" t="s">
         <v>88</v>
-      </c>
-      <c r="I2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K2" t="s">
-        <v>92</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -3331,19 +3362,19 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L3">
         <v>-1</v>
@@ -3351,168 +3382,180 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D16" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D18" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D23" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3523,6 +3566,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3532,7 +3576,7 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.19921875" customWidth="1"/>
     <col min="5" max="5" width="19.19921875" customWidth="1"/>
     <col min="6" max="6" width="26.09765625" customWidth="1"/>
@@ -3572,13 +3616,13 @@
         <v>正位置</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>-1</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -3591,13 +3635,13 @@
         <v>逆位置</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>-1</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -3610,13 +3654,13 @@
         <v>正位置</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>-1</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -3629,13 +3673,13 @@
         <v>逆位置</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>-1</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -3648,13 +3692,13 @@
         <v>正位置</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>-1</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -3667,13 +3711,13 @@
         <v>逆位置</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>-1</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -3686,13 +3730,13 @@
         <v>正位置</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>-1</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -3705,13 +3749,13 @@
         <v>逆位置</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -3724,13 +3768,13 @@
         <v>正位置</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>-1</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3743,13 +3787,13 @@
         <v>逆位置</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>-1</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -3762,13 +3806,13 @@
         <v>正位置</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>-1</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -3781,13 +3825,13 @@
         <v>逆位置</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13">
         <v>-1</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -3800,13 +3844,13 @@
         <v>正位置</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>-1</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -3819,13 +3863,13 @@
         <v>逆位置</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15">
         <v>-1</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -3838,13 +3882,13 @@
         <v>正位置</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16">
         <v>-1</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -3857,13 +3901,13 @@
         <v>逆位置</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17">
         <v>-1</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -3876,13 +3920,13 @@
         <v>正位置</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>-1</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -3895,13 +3939,13 @@
         <v>逆位置</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19">
         <v>-1</v>
       </c>
       <c r="G19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -3914,13 +3958,13 @@
         <v>正位置</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20">
         <v>-1</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3933,13 +3977,13 @@
         <v>逆位置</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>-1</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -3952,13 +3996,13 @@
         <v>正位置</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22">
         <v>-1</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -3971,13 +4015,13 @@
         <v>逆位置</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>-1</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -3990,13 +4034,13 @@
         <v>正位置</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>-1</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -4009,13 +4053,13 @@
         <v>逆位置</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25">
         <v>-1</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -4028,13 +4072,13 @@
         <v>正位置</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26">
         <v>-1</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -4047,13 +4091,13 @@
         <v>逆位置</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>-1</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -4066,13 +4110,13 @@
         <v>正位置</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>-1</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -4085,13 +4129,13 @@
         <v>逆位置</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -4104,13 +4148,13 @@
         <v>正位置</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>-1</v>
       </c>
       <c r="G30" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -4123,13 +4167,13 @@
         <v>逆位置</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31">
         <v>-1</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -4142,13 +4186,13 @@
         <v>正位置</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32">
         <v>-1</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -4161,13 +4205,13 @@
         <v>逆位置</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>-1</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -4180,13 +4224,13 @@
         <v>正位置</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>-1</v>
       </c>
       <c r="G34" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -4199,13 +4243,13 @@
         <v>逆位置</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35">
         <v>-1</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -4218,13 +4262,13 @@
         <v>正位置</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36">
         <v>-1</v>
       </c>
       <c r="G36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -4237,13 +4281,13 @@
         <v>逆位置</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37">
         <v>-1</v>
       </c>
       <c r="G37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -4256,13 +4300,13 @@
         <v>正位置</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38">
         <v>-1</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -4275,13 +4319,13 @@
         <v>逆位置</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39">
         <v>-1</v>
       </c>
       <c r="G39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -4294,13 +4338,13 @@
         <v>正位置</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D40">
         <v>-1</v>
       </c>
       <c r="G40" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -4313,13 +4357,13 @@
         <v>逆位置</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41">
         <v>-1</v>
       </c>
       <c r="G41" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -4332,13 +4376,13 @@
         <v>正位置</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42">
         <v>-1</v>
       </c>
       <c r="G42" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -4351,13 +4395,13 @@
         <v>逆位置</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43">
         <v>-1</v>
       </c>
       <c r="G43" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -4370,13 +4414,13 @@
         <v>正位置</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D44">
         <v>-1</v>
       </c>
       <c r="G44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -4389,13 +4433,13 @@
         <v>逆位置</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D45">
         <v>-1</v>
       </c>
       <c r="G45" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4417,9 +4461,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5627C19-F3CD-46AE-978E-67EFA57D941D}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8635A1E1-DFB5-44EE-B23D-E3135B8EDC4B}">
           <x14:formula1>
-            <xm:f>選択用フィールド!$A$2:$A$4</xm:f>
+            <xm:f>選択用フィールド!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C45</xm:sqref>
         </x14:dataValidation>

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1DAA7A-A263-4CE1-9DCF-DB13D4EDDF88}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B98F86-442A-48B5-96C7-87DD1FC59F87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="99">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -518,10 +518,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Effect/ArcanaSkill</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>効果音名</t>
     <rPh sb="0" eb="4">
       <t>コウカオンメイ</t>
@@ -595,6 +591,14 @@
     <rPh sb="4" eb="6">
       <t>ハツドウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effect/Arcana</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -719,14 +723,14 @@
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="6">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="5">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
-      <calculatedColumnFormula>InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="0">
+      <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
       <calculatedColumnFormula>InputData[[#This Row],[効果音]]</calculatedColumnFormula>
@@ -1584,7 +1588,7 @@
     <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.69921875" customWidth="1"/>
     <col min="9" max="9" width="28.59765625" bestFit="1" customWidth="1"/>
@@ -1640,9 +1644,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F2">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F2" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G2">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1678,9 +1682,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F3">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F3" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G3">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1716,9 +1720,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F4">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F4" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G4">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1748,15 +1752,15 @@
       </c>
       <c r="D5" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E5">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
-      </c>
-      <c r="F5">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F5" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/Monster</v>
       </c>
       <c r="G5">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1792,9 +1796,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F6">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F6" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G6">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1830,9 +1834,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F7">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F7" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G7">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1868,9 +1872,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F8">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F8" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G8">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1906,9 +1910,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F9">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F9" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G9">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1944,9 +1948,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F10">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F10" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G10">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1982,9 +1986,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F11">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F11" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G11">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2020,9 +2024,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F12">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F12" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G12">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2058,9 +2062,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F13">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F13" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G13">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2096,9 +2100,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F14">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F14" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G14">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2134,9 +2138,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F15">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F15" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G15">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2172,9 +2176,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F16">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F16" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G16">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2210,9 +2214,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F17">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F17" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G17">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2248,9 +2252,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F18">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F18" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G18">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2286,9 +2290,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F19">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F19" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G19">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2324,9 +2328,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F20">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F20" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G20">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2362,9 +2366,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F21">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F21" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G21">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2400,9 +2404,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F22">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F22" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G22">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2438,9 +2442,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F23">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F23" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G23">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2476,9 +2480,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F24">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F24" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G24">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2514,9 +2518,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F25">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F25" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G25">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2552,9 +2556,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F26">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F26" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G26">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2590,9 +2594,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F27">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F27" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G27">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2628,9 +2632,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F28">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F28" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G28">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2666,9 +2670,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F29">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F29" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G29">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2704,9 +2708,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F30">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F30" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G30">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2742,9 +2746,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F31">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F31" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G31">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2780,9 +2784,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F32">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F32" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G32">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2818,9 +2822,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F33">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F33" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G33">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2856,9 +2860,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F34">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F34" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G34">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2894,9 +2898,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F35">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F35" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G35">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2932,9 +2936,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F36">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F36" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G36">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2970,9 +2974,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F37">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F37" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G37">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3008,9 +3012,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F38">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F38" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G38">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3046,9 +3050,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F39">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F39" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G39">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3084,9 +3088,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F40">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F40" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G40">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3122,9 +3126,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F41">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F41" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G41">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3160,9 +3164,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F42">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F42" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G42">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3198,9 +3202,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F43">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F43" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G43">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3236,9 +3240,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F44">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F44" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G44">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3274,9 +3278,9 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F45">
-        <f>InputData[[#This Row],[エフェクト]]</f>
-        <v>0</v>
+      <c r="F45" t="str">
+        <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
+        <v>Effect/Arcana/</v>
       </c>
       <c r="G45">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3327,10 +3331,10 @@
         <v>83</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L1" s="2"/>
     </row>
@@ -3339,7 +3343,7 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -3348,13 +3352,13 @@
         <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -3365,7 +3369,7 @@
         <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>38</v>
@@ -3374,7 +3378,7 @@
         <v>61</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L3">
         <v>-1</v>
@@ -3382,10 +3386,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
@@ -3396,10 +3400,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
@@ -3410,10 +3414,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
         <v>41</v>
@@ -3673,10 +3677,13 @@
         <v>逆位置</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
       </c>
       <c r="G5" t="s">
         <v>36</v>

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B98F86-442A-48B5-96C7-87DD1FC59F87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E0EBAF-A26B-496C-A4E8-2088C6E1609D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="141">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -266,13 +266,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HPを1.3倍にしてくれるカード</t>
-    <rPh sb="6" eb="7">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -599,6 +592,433 @@
   </si>
   <si>
     <t>Effect/Arcana</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何も持たなくても勝てることが証明できるカード</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショウメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防御無視を付与できるカード</t>
+    <rPh sb="0" eb="4">
+      <t>ボウギョムシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>召喚物を出せるカード</t>
+    <rPh sb="0" eb="3">
+      <t>ショウカンブツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間がたつほど強くなるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間がたつほど弱くなるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自然治癒を付与するカード</t>
+    <rPh sb="0" eb="4">
+      <t>シゼンチユ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダムでバフやデバフがつくカード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル禁止を付与するカード</t>
+    <rPh sb="3" eb="5">
+      <t>キンシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常攻撃は振れないがダメージが上がるカード</t>
+    <rPh sb="0" eb="4">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキルの当たり判定が大きくなるカード</t>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の行動を逆にするカード</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ギャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵がダメージを肩代わりしてくれるカード</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カタガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分以外の視界を暗くするカード</t>
+    <rPh sb="0" eb="4">
+      <t>ジブンイガイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シカイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>クラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル発動の予備動作の時間が半分になるカード</t>
+    <rPh sb="3" eb="5">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ヨビドウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力を上げるカード</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HPを上げるカード</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HPが減るたび他のステータスが上がるカード</t>
+    <rPh sb="3" eb="4">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人が回復したHPを半分奪うカード</t>
+    <rPh sb="0" eb="1">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ウバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トラップを設置するカード</t>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダムな場所にテレポートするカード</t>
+    <rPh sb="5" eb="7">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵をジャンプ禁止にするカード</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カウンターを付与するカード</t>
+    <rPh sb="6" eb="8">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>視点が反対になるカード</t>
+    <rPh sb="0" eb="2">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運気が上がるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ウンキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手にダメージを与えたときに回復するカード</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のスキルのクールタイムを早くするカード</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のクールタイムを遅くするカード</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のバフ・デバフを消し、その分攻撃力が上がるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タレットがおけるカード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確率で数秒後にスキルが再発動するカード</t>
+    <rPh sb="0" eb="2">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>スウビョウゴ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サイハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたが注目を浴びるカード</t>
+    <rPh sb="4" eb="6">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無敵を付与するカード</t>
+    <rPh sb="0" eb="2">
+      <t>ムテキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>晴れ日和になるカード</t>
+    <rPh sb="0" eb="1">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ビヨリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵をスタンするカード</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銃弾の雨が降ってくるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウダン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アメ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二段ジャンプができるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ニダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次元移動ができるカード</t>
+    <rPh sb="0" eb="4">
+      <t>ジゲンイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度が速くなるカード</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Trap</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Turret</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>miniBullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵に一定のダメージを与えるカード</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アタ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -718,7 +1138,7 @@
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="7">
-      <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</calculatedColumnFormula>
+      <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
@@ -729,16 +1149,16 @@
     <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="5">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -753,7 +1173,7 @@
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="0">
       <calculatedColumnFormula>IF(ArcanaMaster[[#This Row],[位置]]="Front", "正位置", "逆位置")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
@@ -1590,7 +2010,7 @@
     <col min="5" max="5" width="13.19921875" customWidth="1"/>
     <col min="6" max="6" width="20.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.69921875" customWidth="1"/>
+    <col min="8" max="8" width="51.3984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1620,7 +2040,7 @@
         <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1629,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C2" t="str">
@@ -1654,7 +2074,7 @@
       </c>
       <c r="H2" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>HPを1.3倍にしてくれるカード</v>
+        <v>HPを上げるカード</v>
       </c>
       <c r="I2" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1667,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C3" t="str">
@@ -1692,7 +2112,7 @@
       </c>
       <c r="H3" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>何も持たなくても勝てることが証明できるカード</v>
       </c>
       <c r="I3" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A3, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1705,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C4" t="str">
@@ -1730,7 +2150,7 @@
       </c>
       <c r="H4" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>防御無視を付与できるカード</v>
       </c>
       <c r="I4" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A4, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1743,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C5" t="str">
@@ -1756,7 +2176,7 @@
       </c>
       <c r="E5">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F5" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -1768,7 +2188,7 @@
       </c>
       <c r="H5" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>召喚物を出せるカード</v>
       </c>
       <c r="I5" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A5, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1781,7 +2201,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C6" t="str">
@@ -1806,7 +2226,7 @@
       </c>
       <c r="H6" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>時間がたつほど強くなるカード</v>
       </c>
       <c r="I6" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A6, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1819,7 +2239,7 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C7" t="str">
@@ -1844,7 +2264,7 @@
       </c>
       <c r="H7" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>時間がたつほど弱くなるカード</v>
       </c>
       <c r="I7" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A7, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1857,7 +2277,7 @@
         <v>3</v>
       </c>
       <c r="B8">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C8" t="str">
@@ -1882,7 +2302,7 @@
       </c>
       <c r="H8" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>自然治癒を付与するカード</v>
       </c>
       <c r="I8" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A8, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1895,7 +2315,7 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C9" t="str">
@@ -1912,7 +2332,7 @@
       </c>
       <c r="F9" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Dice</v>
       </c>
       <c r="G9">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -1920,7 +2340,7 @@
       </c>
       <c r="H9" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>ランダムでバフやデバフがつくカード</v>
       </c>
       <c r="I9" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A9, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1933,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="B10">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C10" t="str">
@@ -1942,11 +2362,11 @@
       </c>
       <c r="D10" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E10">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="F10" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -1958,7 +2378,7 @@
       </c>
       <c r="H10" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>スキル禁止を付与するカード</v>
       </c>
       <c r="I10" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A10, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -1971,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C11" t="str">
@@ -1996,7 +2416,7 @@
       </c>
       <c r="H11" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>通常攻撃は振れないがダメージが上がるカード</v>
       </c>
       <c r="I11" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A11, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2009,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="B12">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C12" t="str">
@@ -2034,7 +2454,7 @@
       </c>
       <c r="H12" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>スキルの当たり判定が大きくなるカード</v>
       </c>
       <c r="I12" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A12, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2047,7 +2467,7 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C13" t="str">
@@ -2056,11 +2476,11 @@
       </c>
       <c r="D13" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E13">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="F13" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2072,7 +2492,7 @@
       </c>
       <c r="H13" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>敵の行動を逆にするカード</v>
       </c>
       <c r="I13" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A13, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2085,7 +2505,7 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C14" t="str">
@@ -2094,11 +2514,11 @@
       </c>
       <c r="D14" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E14">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="F14" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2110,7 +2530,7 @@
       </c>
       <c r="H14" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>敵がダメージを肩代わりしてくれるカード</v>
       </c>
       <c r="I14" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A14, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2123,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C15" t="str">
@@ -2132,11 +2552,11 @@
       </c>
       <c r="D15" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E15">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>40</v>
       </c>
       <c r="F15" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2148,7 +2568,7 @@
       </c>
       <c r="H15" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>自分以外の視界を暗くするカード</v>
       </c>
       <c r="I15" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A15, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2161,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C16" t="str">
@@ -2186,7 +2606,7 @@
       </c>
       <c r="H16" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>移動速度が速くなるカード</v>
       </c>
       <c r="I16" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A16, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2199,7 +2619,7 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C17" t="str">
@@ -2224,7 +2644,7 @@
       </c>
       <c r="H17" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>スキル発動の予備動作の時間が半分になるカード</v>
       </c>
       <c r="I17" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A17, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2237,7 +2657,7 @@
         <v>8</v>
       </c>
       <c r="B18">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C18" t="str">
@@ -2262,7 +2682,7 @@
       </c>
       <c r="H18" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>攻撃力を上げるカード</v>
       </c>
       <c r="I18" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A18, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2275,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="B19">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C19" t="str">
@@ -2284,7 +2704,7 @@
       </c>
       <c r="D19" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>DamageEffect</v>
       </c>
       <c r="E19">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2300,7 +2720,7 @@
       </c>
       <c r="H19" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>HPが減るたび他のステータスが上がるカード</v>
       </c>
       <c r="I19" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A19, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2313,7 +2733,7 @@
         <v>9</v>
       </c>
       <c r="B20">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C20" t="str">
@@ -2338,7 +2758,7 @@
       </c>
       <c r="H20" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>人が回復したHPを半分奪うカード</v>
       </c>
       <c r="I20" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A20, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2351,7 +2771,7 @@
         <v>9</v>
       </c>
       <c r="B21">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C21" t="str">
@@ -2368,7 +2788,7 @@
       </c>
       <c r="F21" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Trap</v>
       </c>
       <c r="G21">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2376,7 +2796,7 @@
       </c>
       <c r="H21" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>トラップを設置するカード</v>
       </c>
       <c r="I21" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A21, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2389,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="B22">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C22" t="str">
@@ -2398,11 +2818,11 @@
       </c>
       <c r="D22" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E22">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="F22" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2414,7 +2834,7 @@
       </c>
       <c r="H22" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>ランダムな場所にテレポートするカード</v>
       </c>
       <c r="I22" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A22, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2427,7 +2847,7 @@
         <v>10</v>
       </c>
       <c r="B23">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C23" t="str">
@@ -2436,11 +2856,11 @@
       </c>
       <c r="D23" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E23">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="F23" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2452,7 +2872,7 @@
       </c>
       <c r="H23" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>敵をジャンプ禁止にするカード</v>
       </c>
       <c r="I23" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A23, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2465,7 +2885,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C24" t="str">
@@ -2474,11 +2894,11 @@
       </c>
       <c r="D24" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E24">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="F24" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2490,7 +2910,7 @@
       </c>
       <c r="H24" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>敵に一定のダメージを与えるカード</v>
       </c>
       <c r="I24" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A24, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2503,7 +2923,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C25" t="str">
@@ -2512,11 +2932,11 @@
       </c>
       <c r="D25" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E25">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="F25" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2528,7 +2948,7 @@
       </c>
       <c r="H25" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>カウンターを付与するカード</v>
       </c>
       <c r="I25" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A25, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2541,7 +2961,7 @@
         <v>12</v>
       </c>
       <c r="B26">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C26" t="str">
@@ -2550,11 +2970,11 @@
       </c>
       <c r="D26" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E26">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="F26" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2566,7 +2986,7 @@
       </c>
       <c r="H26" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>視点が反対になるカード</v>
       </c>
       <c r="I26" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A26, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2579,7 +2999,7 @@
         <v>12</v>
       </c>
       <c r="B27">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C27" t="str">
@@ -2604,7 +3024,7 @@
       </c>
       <c r="H27" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>運気が上がるカード</v>
       </c>
       <c r="I27" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A27, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2617,7 +3037,7 @@
         <v>13</v>
       </c>
       <c r="B28">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C28" t="str">
@@ -2655,7 +3075,7 @@
         <v>13</v>
       </c>
       <c r="B29">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C29" t="str">
@@ -2664,7 +3084,7 @@
       </c>
       <c r="D29" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>DamageEffect</v>
       </c>
       <c r="E29">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -2680,7 +3100,7 @@
       </c>
       <c r="H29" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>相手にダメージを与えたときに回復するカード</v>
       </c>
       <c r="I29" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A29, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2693,7 +3113,7 @@
         <v>14</v>
       </c>
       <c r="B30">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C30" t="str">
@@ -2718,7 +3138,7 @@
       </c>
       <c r="H30" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>自分のスキルのクールタイムを早くするカード</v>
       </c>
       <c r="I30" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A30, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2731,7 +3151,7 @@
         <v>14</v>
       </c>
       <c r="B31">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C31" t="str">
@@ -2756,7 +3176,7 @@
       </c>
       <c r="H31" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>敵のクールタイムを遅くするカード</v>
       </c>
       <c r="I31" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A31, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2769,7 +3189,7 @@
         <v>15</v>
       </c>
       <c r="B32">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C32" t="str">
@@ -2807,7 +3227,7 @@
         <v>15</v>
       </c>
       <c r="B33">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C33" t="str">
@@ -2816,11 +3236,11 @@
       </c>
       <c r="D33" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E33">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F33" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2832,7 +3252,7 @@
       </c>
       <c r="H33" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>自分のバフ・デバフを消し、その分攻撃力が上がるカード</v>
       </c>
       <c r="I33" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A33, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2845,7 +3265,7 @@
         <v>16</v>
       </c>
       <c r="B34">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C34" t="str">
@@ -2854,15 +3274,15 @@
       </c>
       <c r="D34" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E34">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>90</v>
       </c>
       <c r="F34" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Turret</v>
       </c>
       <c r="G34">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -2870,7 +3290,7 @@
       </c>
       <c r="H34" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>タレットがおけるカード</v>
       </c>
       <c r="I34" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A34, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2883,7 +3303,7 @@
         <v>16</v>
       </c>
       <c r="B35">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C35" t="str">
@@ -2908,7 +3328,7 @@
       </c>
       <c r="H35" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>確率で数秒後にスキルが再発動するカード</v>
       </c>
       <c r="I35" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A35, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2921,7 +3341,7 @@
         <v>17</v>
       </c>
       <c r="B36">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C36" t="str">
@@ -2930,11 +3350,11 @@
       </c>
       <c r="D36" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E36">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>50</v>
       </c>
       <c r="F36" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2946,7 +3366,7 @@
       </c>
       <c r="H36" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>あなたが注目を浴びるカード</v>
       </c>
       <c r="I36" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A36, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2959,7 +3379,7 @@
         <v>17</v>
       </c>
       <c r="B37">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C37" t="str">
@@ -2968,11 +3388,11 @@
       </c>
       <c r="D37" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E37">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="F37" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -2984,7 +3404,7 @@
       </c>
       <c r="H37" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>無敵を付与するカード</v>
       </c>
       <c r="I37" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A37, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -2997,7 +3417,7 @@
         <v>18</v>
       </c>
       <c r="B38">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C38" t="str">
@@ -3035,7 +3455,7 @@
         <v>18</v>
       </c>
       <c r="B39">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C39" t="str">
@@ -3073,7 +3493,7 @@
         <v>19</v>
       </c>
       <c r="B40">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C40" t="str">
@@ -3082,11 +3502,11 @@
       </c>
       <c r="D40" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E40">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="F40" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -3098,7 +3518,7 @@
       </c>
       <c r="H40" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>晴れ日和になるカード</v>
       </c>
       <c r="I40" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A40, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3111,7 +3531,7 @@
         <v>19</v>
       </c>
       <c r="B41">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C41" t="str">
@@ -3120,11 +3540,11 @@
       </c>
       <c r="D41" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E41">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="F41" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -3136,7 +3556,7 @@
       </c>
       <c r="H41" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>敵をスタンするカード</v>
       </c>
       <c r="I41" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A41, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3149,7 +3569,7 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C42" t="str">
@@ -3187,7 +3607,7 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C43" t="str">
@@ -3196,15 +3616,15 @@
       </c>
       <c r="D43" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E43">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="F43" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/miniBullet</v>
       </c>
       <c r="G43">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3212,7 +3632,7 @@
       </c>
       <c r="H43" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>銃弾の雨が降ってくるカード</v>
       </c>
       <c r="I43" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A43, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3225,7 +3645,7 @@
         <v>21</v>
       </c>
       <c r="B44">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="C44" t="str">
@@ -3250,7 +3670,7 @@
       </c>
       <c r="H44" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>二段ジャンプができるカード</v>
       </c>
       <c r="I44" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A44, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3263,7 +3683,7 @@
         <v>21</v>
       </c>
       <c r="B45">
-        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$K$2:$L$3,2,FALSE)</f>
+        <f>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="C45" t="str">
@@ -3288,7 +3708,7 @@
       </c>
       <c r="H45" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>次元移動ができるカード</v>
       </c>
       <c r="I45" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A45, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3307,7 +3727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA57FC-DF38-4EEA-B04B-DBAD106E9B87}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.296875" bestFit="1" customWidth="1"/>
@@ -3315,258 +3735,258 @@
     <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="8.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="2"/>
       <c r="G1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+        <v>82</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K2" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2">
+        <v>86</v>
+      </c>
+      <c r="J2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>33</v>
       </c>
       <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>61</v>
       </c>
-      <c r="K3" t="s">
-        <v>88</v>
-      </c>
-      <c r="L3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>94</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>91</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>39</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="G5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>95</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>92</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D7" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D8" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D9" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D10" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D10" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D11" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D11" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D12" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D13" t="s">
         <v>47</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D13" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D14" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D14" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D15" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D16" t="s">
         <v>50</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3626,7 +4046,7 @@
         <v>-1</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -3645,7 +4065,7 @@
         <v>-1</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -3664,7 +4084,7 @@
         <v>-1</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -3680,13 +4100,13 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -3705,7 +4125,7 @@
         <v>-1</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -3724,7 +4144,7 @@
         <v>-1</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -3743,7 +4163,7 @@
         <v>-1</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -3761,8 +4181,11 @@
       <c r="D9">
         <v>-1</v>
       </c>
+      <c r="E9" t="s">
+        <v>136</v>
+      </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -3775,13 +4198,13 @@
         <v>正位置</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -3800,7 +4223,7 @@
         <v>-1</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -3819,7 +4242,7 @@
         <v>-1</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -3832,13 +4255,13 @@
         <v>逆位置</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -3851,13 +4274,13 @@
         <v>正位置</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -3870,13 +4293,13 @@
         <v>逆位置</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -3895,7 +4318,7 @@
         <v>-1</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -3914,7 +4337,7 @@
         <v>-1</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -3933,7 +4356,7 @@
         <v>-1</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -3946,13 +4369,13 @@
         <v>逆位置</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D19">
         <v>-1</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -3971,7 +4394,7 @@
         <v>-1</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -3989,8 +4412,11 @@
       <c r="D21">
         <v>-1</v>
       </c>
+      <c r="E21" t="s">
+        <v>137</v>
+      </c>
       <c r="G21" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -4003,13 +4429,13 @@
         <v>正位置</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4022,13 +4448,13 @@
         <v>逆位置</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -4041,13 +4467,13 @@
         <v>正位置</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -4060,13 +4486,13 @@
         <v>逆位置</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -4079,13 +4505,13 @@
         <v>正位置</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -4104,7 +4530,7 @@
         <v>-1</v>
       </c>
       <c r="G27" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -4123,7 +4549,7 @@
         <v>-1</v>
       </c>
       <c r="G28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -4136,13 +4562,13 @@
         <v>逆位置</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="G29" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -4161,7 +4587,7 @@
         <v>-1</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -4180,7 +4606,7 @@
         <v>-1</v>
       </c>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -4199,7 +4625,7 @@
         <v>-1</v>
       </c>
       <c r="G32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -4212,13 +4638,13 @@
         <v>逆位置</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -4231,13 +4657,16 @@
         <v>正位置</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>90</v>
+      </c>
+      <c r="E34" t="s">
+        <v>138</v>
       </c>
       <c r="G34" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -4256,7 +4685,7 @@
         <v>-1</v>
       </c>
       <c r="G35" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -4269,13 +4698,13 @@
         <v>正位置</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -4288,13 +4717,13 @@
         <v>逆位置</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -4313,7 +4742,7 @@
         <v>-1</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -4332,7 +4761,7 @@
         <v>-1</v>
       </c>
       <c r="G39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -4345,13 +4774,13 @@
         <v>正位置</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -4364,13 +4793,13 @@
         <v>逆位置</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="G41" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -4389,7 +4818,7 @@
         <v>-1</v>
       </c>
       <c r="G42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -4402,13 +4831,16 @@
         <v>逆位置</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>45</v>
+      </c>
+      <c r="E43" t="s">
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -4427,7 +4859,7 @@
         <v>-1</v>
       </c>
       <c r="G44" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -4446,7 +4878,7 @@
         <v>-1</v>
       </c>
       <c r="G45" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4462,8 +4894,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E0EBAF-A26B-496C-A4E8-2088C6E1609D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8735914-91D8-4A23-992E-FC58E8841D1A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
     <sheet name="ArcanaData" sheetId="2" r:id="rId2"/>
     <sheet name="選択用フィールド" sheetId="4" r:id="rId3"/>
-    <sheet name="InputFile" sheetId="3" r:id="rId4"/>
+    <sheet name="InputFile(Arcana)" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8735914-91D8-4A23-992E-FC58E8841D1A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E499C78-92B4-48DC-82BB-745F89D6A1D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="144">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1018,6 +1018,42 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果時間</t>
+    <rPh sb="0" eb="4">
+      <t>コウカジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果数値</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃を降るたびにダメージを受けるが攻撃力が上がるカード</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1079,7 +1115,10 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1131,34 +1170,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{621B0832-E473-431C-92A8-162988D5197C}" name="ArcanaData" displayName="ArcanaData" ref="A1:I45">
-  <autoFilter ref="A1:I45" xr:uid="{48DDBA56-844D-4376-B3AF-39BFA95D20A0}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{621B0832-E473-431C-92A8-162988D5197C}" name="ArcanaData" displayName="ArcanaData" ref="A1:J45">
+  <autoFilter ref="A1:J45" xr:uid="{48DDBA56-844D-4376-B3AF-39BFA95D20A0}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="8">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="1">
+      <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
       <calculatedColumnFormula>InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1167,9 +1209,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{32B68BED-962F-4870-BA6F-652EF427085D}" name="InputData" displayName="InputData" ref="A1:G45" totalsRowShown="0">
-  <autoFilter ref="A1:G45" xr:uid="{E1D23D5A-3AD7-47D8-AA45-95C0A75F6512}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{32B68BED-962F-4870-BA6F-652EF427085D}" name="InputData" displayName="InputData" ref="A1:H45" totalsRowShown="0">
+  <autoFilter ref="A1:H45" xr:uid="{E1D23D5A-3AD7-47D8-AA45-95C0A75F6512}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
@@ -1178,6 +1220,7 @@
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
     <tableColumn id="4" xr3:uid="{61DC2438-3102-47C3-AF1E-24060A02B3B6}" name="クールタイム"/>
+    <tableColumn id="8" xr3:uid="{F27C3E63-08BA-4AF9-AB67-E53A3623CA44}" name="効果数値"/>
     <tableColumn id="5" xr3:uid="{857F1D44-D30F-42A8-A077-2C649CA34483}" name="エフェクト"/>
     <tableColumn id="6" xr3:uid="{9FDC755C-C1F1-451F-9F56-57E80BEF9975}" name="効果音"/>
     <tableColumn id="7" xr3:uid="{2ABA92AA-D98D-4FD7-A61F-364616B2E89F}" name="説明"/>
@@ -2001,20 +2044,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CB5D73-7EAF-422C-8FF3-EA2211BD96FE}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.19921875" customWidth="1"/>
+    <col min="7" max="7" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2031,19 +2074,22 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2064,24 +2110,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F2">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1.3</v>
+      </c>
+      <c r="G2" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>HPを上げるカード</v>
       </c>
-      <c r="I2" s="1" t="str">
+      <c r="J2" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana00FoolFront</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2102,24 +2152,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G3" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>何も持たなくても勝てることが証明できるカード</v>
       </c>
-      <c r="I3" s="1" t="str">
+      <c r="J3" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A3, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana00FoolBack</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2140,24 +2194,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F4">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G4" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>防御無視を付与できるカード</v>
       </c>
-      <c r="I4" s="1" t="str">
+      <c r="J4" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A4, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana01MagicianFront</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2178,24 +2236,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>30</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F5">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>3</v>
+      </c>
+      <c r="G5" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Monster</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>召喚物を出せるカード</v>
       </c>
-      <c r="I5" s="1" t="str">
+      <c r="J5" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A5, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana01MagicianBack</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2216,24 +2278,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F6">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1.05</v>
+      </c>
+      <c r="G6" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>時間がたつほど強くなるカード</v>
       </c>
-      <c r="I6" s="1" t="str">
+      <c r="J6" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A6, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana02HighPriestessFront</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2254,24 +2320,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F7">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.99</v>
+      </c>
+      <c r="G7" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>時間がたつほど弱くなるカード</v>
       </c>
-      <c r="I7" s="1" t="str">
+      <c r="J7" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A7, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana02HighPriestessBack</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2292,24 +2362,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F8">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>自然治癒を付与するカード</v>
       </c>
-      <c r="I8" s="1" t="str">
+      <c r="J8" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A8, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana03EmpressFront</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2330,24 +2404,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F9">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>20</v>
+      </c>
+      <c r="G9" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Dice</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>ランダムでバフやデバフがつくカード</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="J9" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A9, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana03EmpressBack</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2368,24 +2446,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>60</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F10">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>15</v>
+      </c>
+      <c r="G10" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>スキル禁止を付与するカード</v>
       </c>
-      <c r="I10" s="1" t="str">
+      <c r="J10" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A10, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana04EmperorFront</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2406,24 +2488,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F11">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G11" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>通常攻撃は振れないがダメージが上がるカード</v>
       </c>
-      <c r="I11" s="1" t="str">
+      <c r="J11" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A11, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana04EmperorBack</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2444,24 +2530,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F12">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.3</v>
+      </c>
+      <c r="G12" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>スキルの当たり判定が大きくなるカード</v>
       </c>
-      <c r="I12" s="1" t="str">
+      <c r="J12" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A12, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana05HierophantFront</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2482,24 +2572,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>30</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F13">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>15</v>
+      </c>
+      <c r="G13" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵の行動を逆にするカード</v>
       </c>
-      <c r="I13" s="1" t="str">
+      <c r="J13" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A13, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana05HierophantBack</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -2520,24 +2614,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>30</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F14">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>5</v>
+      </c>
+      <c r="G14" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵がダメージを肩代わりしてくれるカード</v>
       </c>
-      <c r="I14" s="1" t="str">
+      <c r="J14" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A14, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana06LoversFront</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -2558,24 +2656,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>40</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F15">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>10</v>
+      </c>
+      <c r="G15" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>自分以外の視界を暗くするカード</v>
       </c>
-      <c r="I15" s="1" t="str">
+      <c r="J15" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A15, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana06LoversBack</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -2596,24 +2698,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F16">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1.5</v>
+      </c>
+      <c r="G16" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>移動速度が速くなるカード</v>
       </c>
-      <c r="I16" s="1" t="str">
+      <c r="J16" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A16, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana07ChariotFront</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -2634,24 +2740,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F17">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>スキル発動の予備動作の時間が半分になるカード</v>
       </c>
-      <c r="I17" s="1" t="str">
+      <c r="J17" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A17, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana07ChariotBack</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -2672,24 +2782,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F18">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1.2</v>
+      </c>
+      <c r="G18" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>攻撃力を上げるカード</v>
       </c>
-      <c r="I18" s="1" t="str">
+      <c r="J18" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A18, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana08StrengthFront</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -2710,24 +2824,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F19">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.05</v>
+      </c>
+      <c r="G19" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>HPが減るたび他のステータスが上がるカード</v>
       </c>
-      <c r="I19" s="1" t="str">
+      <c r="J19" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A19, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana08StrengthBack</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -2748,24 +2866,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F20">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G20" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>人が回復したHPを半分奪うカード</v>
       </c>
-      <c r="I20" s="1" t="str">
+      <c r="J20" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A20, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana09HermitFront</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -2786,24 +2908,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F21">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>15</v>
+      </c>
+      <c r="G21" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Trap</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>トラップを設置するカード</v>
       </c>
-      <c r="I21" s="1" t="str">
+      <c r="J21" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A21, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana09HermitBack</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -2824,24 +2950,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>15</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F22">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G22" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>ランダムな場所にテレポートするカード</v>
       </c>
-      <c r="I22" s="1" t="str">
+      <c r="J22" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A22, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana10WheelOfFortuneFront</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -2862,24 +2992,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>30</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F23">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>10</v>
+      </c>
+      <c r="G23" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵をジャンプ禁止にするカード</v>
       </c>
-      <c r="I23" s="1" t="str">
+      <c r="J23" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A23, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana10WheelOfFortuneBack</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -2900,24 +3034,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>60</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F24">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>15</v>
+      </c>
+      <c r="G24" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵に一定のダメージを与えるカード</v>
       </c>
-      <c r="I24" s="1" t="str">
+      <c r="J24" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A24, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana11JusticeFront</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -2938,24 +3076,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>30</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F25">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>10</v>
+      </c>
+      <c r="G25" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>カウンターを付与するカード</v>
       </c>
-      <c r="I25" s="1" t="str">
+      <c r="J25" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A25, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana11JusticeBack</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -2976,24 +3118,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>30</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F26">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>5</v>
+      </c>
+      <c r="G26" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>視点が反対になるカード</v>
       </c>
-      <c r="I26" s="1" t="str">
+      <c r="J26" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A26, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana12HangedManFront</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3014,24 +3160,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F27">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G27" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>運気が上がるカード</v>
       </c>
-      <c r="I27" s="1" t="str">
+      <c r="J27" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A27, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana12HangedManBack</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3052,24 +3202,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F28">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>1</v>
+      </c>
+      <c r="G28" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
-      </c>
-      <c r="I28" s="1" t="str">
+        <v>攻撃を降るたびにダメージを受けるが攻撃力が上がるカード</v>
+      </c>
+      <c r="J28" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A28, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana13DeathFront</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3090,24 +3244,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F29">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G29" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>相手にダメージを与えたときに回復するカード</v>
       </c>
-      <c r="I29" s="1" t="str">
+      <c r="J29" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A29, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana13DeathBack</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3128,24 +3286,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F30" t="str">
+      <c r="F30">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.2</v>
+      </c>
+      <c r="G30" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>自分のスキルのクールタイムを早くするカード</v>
       </c>
-      <c r="I30" s="1" t="str">
+      <c r="J30" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A30, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana14TemperanceFront</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3166,24 +3328,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F31" t="str">
+      <c r="F31">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.2</v>
+      </c>
+      <c r="G31" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵のクールタイムを遅くするカード</v>
       </c>
-      <c r="I31" s="1" t="str">
+      <c r="J31" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A31, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana14TemperanceBack</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3204,24 +3370,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F32" t="str">
+      <c r="F32">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G32" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>#</v>
       </c>
-      <c r="I32" s="1" t="str">
+      <c r="J32" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A32, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana15DevilFront</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3242,24 +3412,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>5</v>
       </c>
-      <c r="F33" t="str">
+      <c r="F33">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.05</v>
+      </c>
+      <c r="G33" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>自分のバフ・デバフを消し、その分攻撃力が上がるカード</v>
       </c>
-      <c r="I33" s="1" t="str">
+      <c r="J33" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A33, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana15DevilBack</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3280,24 +3454,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>90</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F34">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G34" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Turret</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H34" t="str">
+      <c r="I34" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>タレットがおけるカード</v>
       </c>
-      <c r="I34" s="1" t="str">
+      <c r="J34" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A34, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana16TowerFront</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3318,24 +3496,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F35" t="str">
+      <c r="F35">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>確率で数秒後にスキルが再発動するカード</v>
       </c>
-      <c r="I35" s="1" t="str">
+      <c r="J35" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A35, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana16TowerBack</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A36">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -3356,24 +3538,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>50</v>
       </c>
-      <c r="F36" t="str">
+      <c r="F36">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>15</v>
+      </c>
+      <c r="G36" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>あなたが注目を浴びるカード</v>
       </c>
-      <c r="I36" s="1" t="str">
+      <c r="J36" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A36, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana17StarFront</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -3394,24 +3580,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>60</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F37">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>5</v>
+      </c>
+      <c r="G37" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H37" t="str">
+      <c r="I37" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>無敵を付与するカード</v>
       </c>
-      <c r="I37" s="1" t="str">
+      <c r="J37" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A37, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana17StarBack</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -3432,24 +3622,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F38">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G38" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H38" t="str">
+      <c r="I38" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>#</v>
       </c>
-      <c r="I38" s="1" t="str">
+      <c r="J38" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A38, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana18MoonFront</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -3470,24 +3664,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F39">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G39" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H39" t="str">
+      <c r="I39" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>#</v>
       </c>
-      <c r="I39" s="1" t="str">
+      <c r="J39" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A39, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana18MoonBack</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -3508,24 +3706,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>45</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F40">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>15</v>
+      </c>
+      <c r="G40" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H40" t="str">
+      <c r="I40" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>晴れ日和になるカード</v>
       </c>
-      <c r="I40" s="1" t="str">
+      <c r="J40" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A40, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana19SunFront</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -3546,24 +3748,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>45</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F41">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>3</v>
+      </c>
+      <c r="G41" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H41" t="str">
+      <c r="I41" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵をスタンするカード</v>
       </c>
-      <c r="I41" s="1" t="str">
+      <c r="J41" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A41, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana19SunBack</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -3584,24 +3790,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F42" t="str">
+      <c r="F42">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G42" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H42" t="str">
+      <c r="I42" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>#</v>
       </c>
-      <c r="I42" s="1" t="str">
+      <c r="J42" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A42, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana20JudgementFront</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A43">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -3622,24 +3832,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>45</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F43">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>3</v>
+      </c>
+      <c r="G43" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/miniBullet</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H43" t="str">
+      <c r="I43" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>銃弾の雨が降ってくるカード</v>
       </c>
-      <c r="I43" s="1" t="str">
+      <c r="J43" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A43, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana20JudgementBack</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A44">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -3660,24 +3874,28 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F44">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G44" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H44" t="str">
+      <c r="I44" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>二段ジャンプができるカード</v>
       </c>
-      <c r="I44" s="1" t="str">
+      <c r="J44" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A44, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana21WorldFront</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -3698,19 +3916,23 @@
         <f>InputData[[#This Row],[クールタイム]]</f>
         <v>-1</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F45">
+        <f>InputData[[#This Row],[効果数値]]</f>
+        <v>-1</v>
+      </c>
+      <c r="G45" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <f>InputData[[#This Row],[効果音]]</f>
         <v>0</v>
       </c>
-      <c r="H45" t="str">
+      <c r="I45" t="str">
         <f>InputData[[#This Row],[説明]]</f>
         <v>次元移動ができるカード</v>
       </c>
-      <c r="I45" s="1" t="str">
+      <c r="J45" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A45, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana21WorldBack</v>
       </c>
@@ -3996,18 +4218,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C49A0F-8337-4201-B700-EC3BC8157248}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" customWidth="1"/>
-    <col min="5" max="5" width="19.19921875" customWidth="1"/>
-    <col min="6" max="6" width="26.09765625" customWidth="1"/>
-    <col min="7" max="7" width="75.8984375" customWidth="1"/>
+    <col min="4" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" customWidth="1"/>
+    <col min="7" max="7" width="26.09765625" customWidth="1"/>
+    <col min="8" max="8" width="75.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4021,16 +4243,19 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4045,11 +4270,14 @@
       <c r="D2">
         <v>-1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E2">
+        <v>1.3</v>
+      </c>
+      <c r="H2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4064,11 +4292,14 @@
       <c r="D3">
         <v>-1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E3">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4083,11 +4314,14 @@
       <c r="D4">
         <v>-1</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4102,14 +4336,17 @@
       <c r="D5">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
         <v>96</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4124,11 +4361,14 @@
       <c r="D6">
         <v>-1</v>
       </c>
-      <c r="G6" t="s">
+      <c r="E6">
+        <v>1.05</v>
+      </c>
+      <c r="H6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4143,11 +4383,14 @@
       <c r="D7">
         <v>-1</v>
       </c>
-      <c r="G7" t="s">
+      <c r="E7">
+        <v>0.99</v>
+      </c>
+      <c r="H7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4162,11 +4405,14 @@
       <c r="D8">
         <v>-1</v>
       </c>
-      <c r="G8" t="s">
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4181,14 +4427,17 @@
       <c r="D9">
         <v>-1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
         <v>136</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4203,11 +4452,14 @@
       <c r="D10">
         <v>60</v>
       </c>
-      <c r="G10" t="s">
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4222,11 +4474,14 @@
       <c r="D11">
         <v>-1</v>
       </c>
-      <c r="G11" t="s">
+      <c r="E11">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -4241,11 +4496,14 @@
       <c r="D12">
         <v>-1</v>
       </c>
-      <c r="G12" t="s">
+      <c r="E12">
+        <v>0.3</v>
+      </c>
+      <c r="H12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -4260,11 +4518,14 @@
       <c r="D13">
         <v>30</v>
       </c>
-      <c r="G13" t="s">
+      <c r="E13">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -4279,11 +4540,14 @@
       <c r="D14">
         <v>30</v>
       </c>
-      <c r="G14" t="s">
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -4298,11 +4562,14 @@
       <c r="D15">
         <v>40</v>
       </c>
-      <c r="G15" t="s">
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -4317,11 +4584,14 @@
       <c r="D16">
         <v>-1</v>
       </c>
-      <c r="G16" t="s">
+      <c r="E16">
+        <v>1.5</v>
+      </c>
+      <c r="H16" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -4336,11 +4606,14 @@
       <c r="D17">
         <v>-1</v>
       </c>
-      <c r="G17" t="s">
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -4355,11 +4628,14 @@
       <c r="D18">
         <v>-1</v>
       </c>
-      <c r="G18" t="s">
+      <c r="E18">
+        <v>1.2</v>
+      </c>
+      <c r="H18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -4374,11 +4650,14 @@
       <c r="D19">
         <v>-1</v>
       </c>
-      <c r="G19" t="s">
+      <c r="E19">
+        <v>0.05</v>
+      </c>
+      <c r="H19" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -4393,11 +4672,14 @@
       <c r="D20">
         <v>-1</v>
       </c>
-      <c r="G20" t="s">
+      <c r="E20">
+        <v>-1</v>
+      </c>
+      <c r="H20" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -4412,14 +4694,17 @@
       <c r="D21">
         <v>-1</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
         <v>137</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -4434,11 +4719,14 @@
       <c r="D22">
         <v>15</v>
       </c>
-      <c r="G22" t="s">
+      <c r="E22">
+        <v>-1</v>
+      </c>
+      <c r="H22" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -4453,11 +4741,14 @@
       <c r="D23">
         <v>30</v>
       </c>
-      <c r="G23" t="s">
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -4472,11 +4763,14 @@
       <c r="D24">
         <v>60</v>
       </c>
-      <c r="G24" t="s">
+      <c r="E24">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -4491,11 +4785,14 @@
       <c r="D25">
         <v>30</v>
       </c>
-      <c r="G25" t="s">
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -4510,11 +4807,14 @@
       <c r="D26">
         <v>30</v>
       </c>
-      <c r="G26" t="s">
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="H26" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -4529,11 +4829,14 @@
       <c r="D27">
         <v>-1</v>
       </c>
-      <c r="G27" t="s">
+      <c r="E27">
+        <v>-1</v>
+      </c>
+      <c r="H27" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -4548,11 +4851,14 @@
       <c r="D28">
         <v>-1</v>
       </c>
-      <c r="G28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -4567,11 +4873,14 @@
       <c r="D29">
         <v>-1</v>
       </c>
-      <c r="G29" t="s">
+      <c r="E29">
+        <v>-1</v>
+      </c>
+      <c r="H29" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -4586,11 +4895,14 @@
       <c r="D30">
         <v>-1</v>
       </c>
-      <c r="G30" t="s">
+      <c r="E30">
+        <v>0.2</v>
+      </c>
+      <c r="H30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -4605,11 +4917,14 @@
       <c r="D31">
         <v>-1</v>
       </c>
-      <c r="G31" t="s">
+      <c r="E31">
+        <v>0.2</v>
+      </c>
+      <c r="H31" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -4624,11 +4939,14 @@
       <c r="D32">
         <v>-1</v>
       </c>
-      <c r="G32" t="s">
+      <c r="E32">
+        <v>-1</v>
+      </c>
+      <c r="H32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -4643,11 +4961,14 @@
       <c r="D33">
         <v>5</v>
       </c>
-      <c r="G33" t="s">
+      <c r="E33">
+        <v>0.05</v>
+      </c>
+      <c r="H33" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -4662,14 +4983,17 @@
       <c r="D34">
         <v>90</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34">
+        <v>-1</v>
+      </c>
+      <c r="F34" t="s">
         <v>138</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -4684,11 +5008,14 @@
       <c r="D35">
         <v>-1</v>
       </c>
-      <c r="G35" t="s">
+      <c r="E35">
+        <v>0.5</v>
+      </c>
+      <c r="H35" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -4703,11 +5030,14 @@
       <c r="D36">
         <v>50</v>
       </c>
-      <c r="G36" t="s">
+      <c r="E36">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -4722,11 +5052,14 @@
       <c r="D37">
         <v>60</v>
       </c>
-      <c r="G37" t="s">
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="H37" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -4741,11 +5074,14 @@
       <c r="D38">
         <v>-1</v>
       </c>
-      <c r="G38" t="s">
+      <c r="E38">
+        <v>-1</v>
+      </c>
+      <c r="H38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -4760,11 +5096,14 @@
       <c r="D39">
         <v>-1</v>
       </c>
-      <c r="G39" t="s">
+      <c r="E39">
+        <v>-1</v>
+      </c>
+      <c r="H39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -4779,11 +5118,14 @@
       <c r="D40">
         <v>45</v>
       </c>
-      <c r="G40" t="s">
+      <c r="E40">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -4798,11 +5140,14 @@
       <c r="D41">
         <v>45</v>
       </c>
-      <c r="G41" t="s">
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="H41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -4817,11 +5162,14 @@
       <c r="D42">
         <v>-1</v>
       </c>
-      <c r="G42" t="s">
+      <c r="E42">
+        <v>-1</v>
+      </c>
+      <c r="H42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -4836,14 +5184,17 @@
       <c r="D43">
         <v>45</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43" t="s">
         <v>139</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -4858,11 +5209,14 @@
       <c r="D44">
         <v>-1</v>
       </c>
-      <c r="G44" t="s">
+      <c r="E44">
+        <v>-1</v>
+      </c>
+      <c r="H44" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -4877,20 +5231,72 @@
       <c r="D45">
         <v>-1</v>
       </c>
-      <c r="G45" t="s">
+      <c r="E45">
+        <v>-1</v>
+      </c>
+      <c r="H45" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="1"/>
-  <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D45" xr:uid="{3D03E15D-E7ED-4977-BF66-D8407C5381AF}">
+  <dataValidations xWindow="629" yWindow="502" count="14">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D45 E29:E34 E3 E10:E11 E13:E15 E17:E18 E20:E27 E36:E42 E44:E45" xr:uid="{3D03E15D-E7ED-4977-BF66-D8407C5381AF}">
       <formula1>-1</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G45" xr:uid="{EE204BD4-67A7-473F-935A-110779F70780}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H45" xr:uid="{EE204BD4-67A7-473F-935A-110779F70780}">
       <formula1>0</formula1>
       <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="入力時" prompt="ここには確率を入れます" sqref="E35" xr:uid="{0FCD90F8-1F94-4A7C-AFCC-A27DD915004E}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="HPの倍率を入力する（例：1.2）" sqref="E2" xr:uid="{8D1A4188-7C47-454B-82F3-D357F7A1EB98}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="召喚物の数を入力" sqref="E5" xr:uid="{BB5C5E15-7BD8-4EBE-B873-D4E01773B168}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="攻撃力の上がる倍率" sqref="E6" xr:uid="{4227E945-1310-4BA3-A745-2433CB6DA9DA}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="攻撃力の下がる倍率" sqref="E7" xr:uid="{0EB4C438-55C2-4335-BAB1-42A5A7F00656}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="回復の数値" sqref="E8" xr:uid="{70CA7073-8536-4256-A7B7-087AFEEE07EE}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="効果を変える時間" sqref="E9" xr:uid="{36D824CD-2529-4A70-9B8B-37593FD58AC4}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="当たり判定のサイズの倍率" sqref="E12" xr:uid="{FFF68715-331B-484F-8BA1-9CA32CB3335F}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="速度の倍率" sqref="E16" xr:uid="{5392813C-5A31-4407-B1FE-DE249FA47D1C}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="上がるダメージの数値" sqref="E19" xr:uid="{5ABDEF00-64F6-4E94-BEB1-657E693B54AB}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="受けるダメージ数" sqref="E28" xr:uid="{C5C15357-CD8F-4186-A078-86CCBF6ADCB5}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="降らせる時間" sqref="E43" xr:uid="{6AE1301C-9383-4835-AD80-4932975FF516}">
+      <formula1>-1</formula1>
+      <formula2>300</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4900,7 +5306,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="629" yWindow="502" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8635A1E1-DFB5-44EE-B23D-E3135B8EDC4B}">
           <x14:formula1>
             <xm:f>選択用フィールド!$A$2:$A$6</xm:f>

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E499C78-92B4-48DC-82BB-745F89D6A1D0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACE4AC6-5EC3-4C07-A2D1-354BE0BB6C9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="148">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1055,6 +1055,43 @@
     <rPh sb="21" eb="22">
       <t>ア</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HpBullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たると現在HPの30％のHPを減らす弾を打つ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分身が出てくるカード</t>
+    <rPh sb="0" eb="2">
+      <t>ブンシン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Clone</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1188,19 +1225,19 @@
     <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="5">
       <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3662,15 +3699,15 @@
       </c>
       <c r="E39">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="F39">
         <f>InputData[[#This Row],[効果数値]]</f>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G39" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Clone</v>
       </c>
       <c r="H39">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3678,7 +3715,7 @@
       </c>
       <c r="I39" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>分身が出てくるカード</v>
       </c>
       <c r="J39" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A39, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3784,19 +3821,19 @@
       </c>
       <c r="D42" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E42">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="F42">
         <f>InputData[[#This Row],[効果数値]]</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/HpBullet</v>
       </c>
       <c r="H42">
         <f>InputData[[#This Row],[効果音]]</f>
@@ -3804,7 +3841,7 @@
       </c>
       <c r="I42" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>当たると現在HPの30％のHPを減らす弾を打つ</v>
       </c>
       <c r="J42" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A42, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -5094,13 +5131,16 @@
         <v>34</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>45</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>3</v>
+      </c>
+      <c r="F39" t="s">
+        <v>147</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
@@ -5157,16 +5197,19 @@
         <v>正位置</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
+        <v>144</v>
       </c>
       <c r="H42" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACE4AC6-5EC3-4C07-A2D1-354BE0BB6C9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA3B154-9547-4BC5-A30A-524A5B0F03A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="F25">
         <f>InputData[[#This Row],[効果数値]]</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -4823,7 +4823,7 @@
         <v>30</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
         <v>119</v>

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA3B154-9547-4BC5-A30A-524A5B0F03A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE45D6E-92E7-42BE-B12E-930548287ED7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="151">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1092,6 +1092,24 @@
   </si>
   <si>
     <t>Clone</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像名</t>
+    <rPh sb="0" eb="3">
+      <t>ガゾウメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sprites/Arcana</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1152,7 +1170,13 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1200,45 +1224,50 @@
     <tableColumn id="1" xr3:uid="{65175C44-F81B-4B6B-B85A-4B77B2D8D94C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C1D039E5-540F-4BA0-A810-85236C0CDD0E}" name="位置"/>
     <tableColumn id="3" xr3:uid="{6BE0F20E-0384-4641-936C-55C7A196FF36}" name="名前"/>
-    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像"/>
+    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="10">
+      <calculatedColumnFormula>TEXT(A2, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{621B0832-E473-431C-92A8-162988D5197C}" name="ArcanaData" displayName="ArcanaData" ref="A1:J45">
-  <autoFilter ref="A1:J45" xr:uid="{48DDBA56-844D-4376-B3AF-39BFA95D20A0}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{621B0832-E473-431C-92A8-162988D5197C}" name="ArcanaData" displayName="ArcanaData" ref="A1:K45">
+  <autoFilter ref="A1:K45" xr:uid="{48DDBA56-844D-4376-B3AF-39BFA95D20A0}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="9">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="8">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="7">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
       <calculatedColumnFormula>InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="1">
+      <calculatedColumnFormula>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1595,6 +1624,10 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2" t="str">
+        <f>TEXT(A2, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>00Fool</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -1606,6 +1639,10 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
+      <c r="D3" t="str">
+        <f>TEXT(A3, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>00Fool</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -1617,6 +1654,10 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
+      <c r="D4" t="str">
+        <f>TEXT(A4, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>01Magician</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -1628,6 +1669,10 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
+      <c r="D5" t="str">
+        <f>TEXT(A5, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>01Magician</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -1639,6 +1684,10 @@
       <c r="C6" t="s">
         <v>12</v>
       </c>
+      <c r="D6" t="str">
+        <f>TEXT(A6, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>02HighPriestess</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -1650,6 +1699,10 @@
       <c r="C7" t="s">
         <v>12</v>
       </c>
+      <c r="D7" t="str">
+        <f>TEXT(A7, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>02HighPriestess</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -1661,6 +1714,10 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
+      <c r="D8" t="str">
+        <f>TEXT(A8, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>03Empress</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -1672,6 +1729,10 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
+      <c r="D9" t="str">
+        <f>TEXT(A9, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>03Empress</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -1683,6 +1744,10 @@
       <c r="C10" t="s">
         <v>14</v>
       </c>
+      <c r="D10" t="str">
+        <f>TEXT(A10, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>04Emperor</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -1694,6 +1759,10 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
+      <c r="D11" t="str">
+        <f>TEXT(A11, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>04Emperor</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -1705,6 +1774,10 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
+      <c r="D12" t="str">
+        <f>TEXT(A12, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>05Hierophant</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -1716,6 +1789,10 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
+      <c r="D13" t="str">
+        <f>TEXT(A13, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>05Hierophant</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
@@ -1727,6 +1804,10 @@
       <c r="C14" t="s">
         <v>16</v>
       </c>
+      <c r="D14" t="str">
+        <f>TEXT(A14, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>06Lovers</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -1738,6 +1819,10 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
+      <c r="D15" t="str">
+        <f>TEXT(A15, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>06Lovers</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -1749,8 +1834,12 @@
       <c r="C16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D16" t="str">
+        <f>TEXT(A16, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>07Chariot</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>7</v>
       </c>
@@ -1760,8 +1849,12 @@
       <c r="C17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D17" t="str">
+        <f>TEXT(A17, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>07Chariot</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1771,8 +1864,12 @@
       <c r="C18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D18" t="str">
+        <f>TEXT(A18, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>08Strength</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>8</v>
       </c>
@@ -1782,8 +1879,12 @@
       <c r="C19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D19" t="str">
+        <f>TEXT(A19, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>08Strength</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1793,8 +1894,12 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D20" t="str">
+        <f>TEXT(A20, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>09Hermit</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>9</v>
       </c>
@@ -1804,8 +1909,12 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D21" t="str">
+        <f>TEXT(A21, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>09Hermit</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>10</v>
       </c>
@@ -1815,8 +1924,12 @@
       <c r="C22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D22" t="str">
+        <f>TEXT(A22, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>10WheelOfFortune</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>10</v>
       </c>
@@ -1826,8 +1939,12 @@
       <c r="C23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D23" t="str">
+        <f>TEXT(A23, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>10WheelOfFortune</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>11</v>
       </c>
@@ -1837,8 +1954,12 @@
       <c r="C24" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D24" t="str">
+        <f>TEXT(A24, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>11Justice</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>11</v>
       </c>
@@ -1848,8 +1969,12 @@
       <c r="C25" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D25" t="str">
+        <f>TEXT(A25, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>11Justice</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>12</v>
       </c>
@@ -1859,8 +1984,12 @@
       <c r="C26" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D26" t="str">
+        <f>TEXT(A26, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>12HangedMan</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>12</v>
       </c>
@@ -1870,8 +1999,12 @@
       <c r="C27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D27" t="str">
+        <f>TEXT(A27, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>12HangedMan</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>13</v>
       </c>
@@ -1881,8 +2014,12 @@
       <c r="C28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D28" t="str">
+        <f>TEXT(A28, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>13Death</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>13</v>
       </c>
@@ -1892,8 +2029,12 @@
       <c r="C29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D29" t="str">
+        <f>TEXT(A29, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>13Death</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>14</v>
       </c>
@@ -1903,8 +2044,12 @@
       <c r="C30" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D30" t="str">
+        <f>TEXT(A30, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>14Temperance</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>14</v>
       </c>
@@ -1914,8 +2059,12 @@
       <c r="C31" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D31" t="str">
+        <f>TEXT(A31, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>14Temperance</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>15</v>
       </c>
@@ -1925,8 +2074,12 @@
       <c r="C32" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D32" t="str">
+        <f>TEXT(A32, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>15Devil</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>15</v>
       </c>
@@ -1936,8 +2089,12 @@
       <c r="C33" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D33" t="str">
+        <f>TEXT(A33, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>15Devil</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>16</v>
       </c>
@@ -1947,8 +2104,12 @@
       <c r="C34" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D34" t="str">
+        <f>TEXT(A34, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>16Tower</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>16</v>
       </c>
@@ -1958,8 +2119,12 @@
       <c r="C35" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D35" t="str">
+        <f>TEXT(A35, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>16Tower</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>17</v>
       </c>
@@ -1969,8 +2134,12 @@
       <c r="C36" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D36" t="str">
+        <f>TEXT(A36, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>17Star</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -1980,8 +2149,12 @@
       <c r="C37" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D37" t="str">
+        <f>TEXT(A37, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>17Star</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>18</v>
       </c>
@@ -1991,8 +2164,12 @@
       <c r="C38" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D38" t="str">
+        <f>TEXT(A38, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>18Moon</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2002,8 +2179,12 @@
       <c r="C39" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D39" t="str">
+        <f>TEXT(A39, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>18Moon</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>19</v>
       </c>
@@ -2013,8 +2194,12 @@
       <c r="C40" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D40" t="str">
+        <f>TEXT(A40, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>19Sun</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>19</v>
       </c>
@@ -2024,8 +2209,12 @@
       <c r="C41" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D41" t="str">
+        <f>TEXT(A41, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>19Sun</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>20</v>
       </c>
@@ -2035,8 +2224,12 @@
       <c r="C42" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D42" t="str">
+        <f>TEXT(A42, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>20Judgement</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>20</v>
       </c>
@@ -2046,8 +2239,12 @@
       <c r="C43" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D43" t="str">
+        <f>TEXT(A43, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>20Judgement</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>21</v>
       </c>
@@ -2057,8 +2254,12 @@
       <c r="C44" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D44" t="str">
+        <f>TEXT(A44, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>21World</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>21</v>
       </c>
@@ -2067,6 +2268,10 @@
       </c>
       <c r="C45" t="s">
         <v>31</v>
+      </c>
+      <c r="D45" t="str">
+        <f>TEXT(A45, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</f>
+        <v>21World</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CB5D73-7EAF-422C-8FF3-EA2211BD96FE}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
@@ -2092,9 +2297,10 @@
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2125,8 +2331,11 @@
       <c r="J1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2167,8 +2376,12 @@
         <f>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana00FoolFront</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K2" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/00Fool</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2209,8 +2422,12 @@
         <f>"Arcana"&amp;TEXT(A3, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana00FoolBack</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K3" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/00Fool</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2251,8 +2468,12 @@
         <f>"Arcana"&amp;TEXT(A4, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana01MagicianFront</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K4" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/01Magician</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2293,8 +2514,12 @@
         <f>"Arcana"&amp;TEXT(A5, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana01MagicianBack</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K5" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/01Magician</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2335,8 +2560,12 @@
         <f>"Arcana"&amp;TEXT(A6, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana02HighPriestessFront</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K6" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/02HighPriestess</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2377,8 +2606,12 @@
         <f>"Arcana"&amp;TEXT(A7, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana02HighPriestessBack</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K7" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/02HighPriestess</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2419,8 +2652,12 @@
         <f>"Arcana"&amp;TEXT(A8, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana03EmpressFront</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K8" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/03Empress</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2461,8 +2698,12 @@
         <f>"Arcana"&amp;TEXT(A9, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana03EmpressBack</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K9" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/03Empress</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2503,8 +2744,12 @@
         <f>"Arcana"&amp;TEXT(A10, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana04EmperorFront</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K10" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/04Emperor</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2545,8 +2790,12 @@
         <f>"Arcana"&amp;TEXT(A11, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana04EmperorBack</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K11" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/04Emperor</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2587,8 +2836,12 @@
         <f>"Arcana"&amp;TEXT(A12, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana05HierophantFront</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K12" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/05Hierophant</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2629,8 +2882,12 @@
         <f>"Arcana"&amp;TEXT(A13, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana05HierophantBack</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K13" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/05Hierophant</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -2671,8 +2928,12 @@
         <f>"Arcana"&amp;TEXT(A14, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana06LoversFront</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K14" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/06Lovers</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -2713,8 +2974,12 @@
         <f>"Arcana"&amp;TEXT(A15, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana06LoversBack</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K15" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/06Lovers</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -2755,8 +3020,12 @@
         <f>"Arcana"&amp;TEXT(A16, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana07ChariotFront</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K16" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/07Chariot</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -2797,8 +3066,12 @@
         <f>"Arcana"&amp;TEXT(A17, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana07ChariotBack</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K17" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/07Chariot</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -2839,8 +3112,12 @@
         <f>"Arcana"&amp;TEXT(A18, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana08StrengthFront</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K18" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/08Strength</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -2881,8 +3158,12 @@
         <f>"Arcana"&amp;TEXT(A19, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana08StrengthBack</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K19" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/08Strength</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -2923,8 +3204,12 @@
         <f>"Arcana"&amp;TEXT(A20, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana09HermitFront</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K20" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/09Hermit</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -2965,8 +3250,12 @@
         <f>"Arcana"&amp;TEXT(A21, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana09HermitBack</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K21" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/09Hermit</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3007,8 +3296,12 @@
         <f>"Arcana"&amp;TEXT(A22, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana10WheelOfFortuneFront</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K22" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/10WheelOfFortune</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3049,8 +3342,12 @@
         <f>"Arcana"&amp;TEXT(A23, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana10WheelOfFortuneBack</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K23" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/10WheelOfFortune</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3091,8 +3388,12 @@
         <f>"Arcana"&amp;TEXT(A24, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana11JusticeFront</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K24" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/11Justice</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3133,8 +3434,12 @@
         <f>"Arcana"&amp;TEXT(A25, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana11JusticeBack</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K25" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/11Justice</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3175,8 +3480,12 @@
         <f>"Arcana"&amp;TEXT(A26, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana12HangedManFront</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K26" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/12HangedMan</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3217,8 +3526,12 @@
         <f>"Arcana"&amp;TEXT(A27, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana12HangedManBack</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K27" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/12HangedMan</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3259,8 +3572,12 @@
         <f>"Arcana"&amp;TEXT(A28, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana13DeathFront</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K28" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/13Death</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3301,8 +3618,12 @@
         <f>"Arcana"&amp;TEXT(A29, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana13DeathBack</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K29" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/13Death</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3343,8 +3664,12 @@
         <f>"Arcana"&amp;TEXT(A30, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana14TemperanceFront</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K30" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/14Temperance</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3385,8 +3710,12 @@
         <f>"Arcana"&amp;TEXT(A31, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana14TemperanceBack</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K31" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/14Temperance</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3427,8 +3756,12 @@
         <f>"Arcana"&amp;TEXT(A32, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana15DevilFront</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K32" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/15Devil</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3469,8 +3802,12 @@
         <f>"Arcana"&amp;TEXT(A33, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana15DevilBack</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K33" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/15Devil</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3511,8 +3848,12 @@
         <f>"Arcana"&amp;TEXT(A34, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana16TowerFront</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K34" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/16Tower</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3553,8 +3894,12 @@
         <f>"Arcana"&amp;TEXT(A35, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana16TowerBack</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K35" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/16Tower</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -3595,8 +3940,12 @@
         <f>"Arcana"&amp;TEXT(A36, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana17StarFront</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K36" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/17Star</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -3637,8 +3986,12 @@
         <f>"Arcana"&amp;TEXT(A37, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana17StarBack</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K37" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/17Star</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -3679,8 +4032,12 @@
         <f>"Arcana"&amp;TEXT(A38, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana18MoonFront</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K38" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/18Moon</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -3721,8 +4078,12 @@
         <f>"Arcana"&amp;TEXT(A39, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana18MoonBack</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K39" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/18Moon</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -3763,8 +4124,12 @@
         <f>"Arcana"&amp;TEXT(A40, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana19SunFront</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K40" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/19Sun</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -3805,8 +4170,12 @@
         <f>"Arcana"&amp;TEXT(A41, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana19SunBack</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K41" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/19Sun</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -3847,8 +4216,12 @@
         <f>"Arcana"&amp;TEXT(A42, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana20JudgementFront</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K42" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/20Judgement</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -3889,8 +4262,12 @@
         <f>"Arcana"&amp;TEXT(A43, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana20JudgementBack</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K43" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/20Judgement</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -3931,8 +4308,12 @@
         <f>"Arcana"&amp;TEXT(A44, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana21WorldFront</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K44" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/21World</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -3972,6 +4353,10 @@
       <c r="J45" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A45, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana21WorldBack</v>
+      </c>
+      <c r="K45" s="1" t="str">
+        <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
+        <v>Sprites/Arcana/21World</v>
       </c>
     </row>
   </sheetData>
@@ -4112,6 +4497,9 @@
       <c r="E7" t="s">
         <v>64</v>
       </c>
+      <c r="G7" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D8" t="s">
@@ -4119,6 +4507,9 @@
       </c>
       <c r="E8" t="s">
         <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE45D6E-92E7-42BE-B12E-930548287ED7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E065CCF-3E32-4E15-A28F-713B4BF7D198}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="2" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -2275,6 +2275,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="kqFsht2GfRnDKTEeWdppLLXHDvtmokHk/KhrW2GTyirUIOrjkvzfmaC6A7hN+Af0l4obuEvLmqYhQznVp4BqFA==" saltValue="dwhLeq6Twhhtt52XYZnitg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4360,6 +4361,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="JsrtSVZYWtqsM+vamaxfnwW6KDjeS8ergY52B5KFDixxAV12yOMwOn788B5MD0Sk+4SDCfMYuevizTiAWnTLKw==" saltValue="oS2zEMxPdy3ezhGbJolCfw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4633,6 +4635,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="ryhF4kBA1BKUHN6LbZlBRteHtUgn49kD1H5CK0aTR961ZyZ07Rj4y9OBolArIZYra1E+Cy2bdg1LYF+iYoq1yg==" saltValue="PerIWNDmBJOSMcG9n1sgIg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>

--- a/Assets/_Project/Excel/ArcanaData.xlsx
+++ b/Assets/_Project/Excel/ArcanaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E065CCF-3E32-4E15-A28F-713B4BF7D198}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DE0F8B-4C90-4557-970E-B2865BBE5ACB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="2" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
